--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3892"/>
+  <dimension ref="A1:E3894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105500,6 +105500,60 @@
         </is>
       </c>
     </row>
+    <row r="3893">
+      <c r="A3893" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B3893" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3893" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3893" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3893" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3894" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3894" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3894" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3894" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3894"/>
+  <dimension ref="A1:E3895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105554,6 +105554,33 @@
         </is>
       </c>
     </row>
+    <row r="3895">
+      <c r="A3895" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3895" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3895" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3895" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3895" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3895"/>
+  <dimension ref="A1:E3896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105581,6 +105581,33 @@
         </is>
       </c>
     </row>
+    <row r="3896">
+      <c r="A3896" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3896" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3896" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D3896" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3896" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3896"/>
+  <dimension ref="A1:E3898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105608,6 +105608,60 @@
         </is>
       </c>
     </row>
+    <row r="3897">
+      <c r="A3897" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B3897" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3897" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3897" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3897" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3898" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3898" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3898" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3898" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3898"/>
+  <dimension ref="A1:E3899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105662,6 +105662,33 @@
         </is>
       </c>
     </row>
+    <row r="3899">
+      <c r="A3899" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3899" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3899" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D3899" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3899" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3899"/>
+  <dimension ref="A1:E3900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105689,6 +105689,33 @@
         </is>
       </c>
     </row>
+    <row r="3900">
+      <c r="A3900" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3900" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3900" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3900" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3900" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3900"/>
+  <dimension ref="A1:E3902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105716,6 +105716,60 @@
         </is>
       </c>
     </row>
+    <row r="3901">
+      <c r="A3901" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3901" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3901" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3901" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3901" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3902" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3902" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3902" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3902" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3902"/>
+  <dimension ref="A1:E3903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105770,6 +105770,33 @@
         </is>
       </c>
     </row>
+    <row r="3903">
+      <c r="A3903" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3903" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3903" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D3903" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3903" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3903"/>
+  <dimension ref="A1:E3904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105797,6 +105797,33 @@
         </is>
       </c>
     </row>
+    <row r="3904">
+      <c r="A3904" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3904" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3904" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3904" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3904" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3904"/>
+  <dimension ref="A1:E3906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -105821,6 +105833,60 @@
       <c r="E3904" t="inlineStr">
         <is>
           <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3905" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3905" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3905" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3905" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3906" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3906" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D3906" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3906" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3906"/>
+  <dimension ref="A1:E3907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105890,6 +105890,33 @@
         </is>
       </c>
     </row>
+    <row r="3907">
+      <c r="A3907" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3907" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3907" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3907" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3907" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3907"/>
+  <dimension ref="A1:E3908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105917,6 +105917,33 @@
         </is>
       </c>
     </row>
+    <row r="3908">
+      <c r="A3908" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3908" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3908" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3908" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3908" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3908"/>
+  <dimension ref="A1:E3910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105944,6 +105944,60 @@
         </is>
       </c>
     </row>
+    <row r="3909">
+      <c r="A3909" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3909" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3909" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3909" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3909" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="3910">
+      <c r="A3910" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3910" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3910" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3910" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3910" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3910"/>
+  <dimension ref="A1:E3911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105998,6 +105998,33 @@
         </is>
       </c>
     </row>
+    <row r="3911">
+      <c r="A3911" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3911" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3911" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D3911" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3911" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3911"/>
+  <dimension ref="A1:E3912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106025,6 +106025,33 @@
         </is>
       </c>
     </row>
+    <row r="3912">
+      <c r="A3912" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3912" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3912" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D3912" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3912" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3912"/>
+  <dimension ref="A1:E3914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106052,6 +106052,60 @@
         </is>
       </c>
     </row>
+    <row r="3913">
+      <c r="A3913" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B3913" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3913" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D3913" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3913" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="3914">
+      <c r="A3914" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3914" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3914" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3914" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E3914" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3914"/>
+  <dimension ref="A1:E3915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106106,6 +106106,33 @@
         </is>
       </c>
     </row>
+    <row r="3915">
+      <c r="A3915" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3915" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3915" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3915" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3915" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3915"/>
+  <dimension ref="A1:E3916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106133,6 +106133,33 @@
         </is>
       </c>
     </row>
+    <row r="3916">
+      <c r="A3916" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3916" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3916" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3916" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3916" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3916"/>
+  <dimension ref="A1:E3918"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106160,6 +106160,60 @@
         </is>
       </c>
     </row>
+    <row r="3917">
+      <c r="A3917" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B3917" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3917" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3917" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E3917" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3918">
+      <c r="A3918" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3918" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3918" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D3918" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3918" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3918"/>
+  <dimension ref="A1:E3919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106214,6 +106214,33 @@
         </is>
       </c>
     </row>
+    <row r="3919">
+      <c r="A3919" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3919" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3919" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3919" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E3919" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3919"/>
+  <dimension ref="A1:E3920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106241,6 +106241,33 @@
         </is>
       </c>
     </row>
+    <row r="3920">
+      <c r="A3920" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3920" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3920" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3920" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3920" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3920"/>
+  <dimension ref="A1:E3922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106268,6 +106268,60 @@
         </is>
       </c>
     </row>
+    <row r="3921">
+      <c r="A3921" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B3921" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3921" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3921" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3921" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3922">
+      <c r="A3922" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3922" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3922" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D3922" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3922" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3922"/>
+  <dimension ref="A1:E3923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106322,6 +106322,33 @@
         </is>
       </c>
     </row>
+    <row r="3923">
+      <c r="A3923" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3923" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3923" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D3923" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3923" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3923"/>
+  <dimension ref="A1:E3924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106349,6 +106349,33 @@
         </is>
       </c>
     </row>
+    <row r="3924">
+      <c r="A3924" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3924" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3924" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D3924" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3924" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3924"/>
+  <dimension ref="A1:E3926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106376,6 +106376,60 @@
         </is>
       </c>
     </row>
+    <row r="3925">
+      <c r="A3925" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B3925" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3925" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3925" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3925" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="3926">
+      <c r="A3926" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B3926" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3926" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3926" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E3926" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3926"/>
+  <dimension ref="A1:E3927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106430,6 +106430,33 @@
         </is>
       </c>
     </row>
+    <row r="3927">
+      <c r="A3927" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B3927" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3927" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3927" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3927" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
